--- a/Lab04/Data/Measurements.xlsx
+++ b/Lab04/Data/Measurements.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/g_tec/Git/EEK_lab/Lab04/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0E9E968-7EE4-F345-BB8D-0E10515902CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5C6D034-753B-0A42-A639-FCC2B127C5AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20560" yWindow="800" windowWidth="20580" windowHeight="24140" xr2:uid="{8B18A92B-45BE-2647-98DB-1FAE42B77EAC}"/>
+    <workbookView xWindow="10260" yWindow="800" windowWidth="20580" windowHeight="24140" xr2:uid="{8B18A92B-45BE-2647-98DB-1FAE42B77EAC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="70">
   <si>
     <t>Part1:</t>
   </si>
@@ -149,12 +149,6 @@
     <t>Q2</t>
   </si>
   <si>
-    <t xml:space="preserve"> \left\{  \left\{ I_{D} = 0.0008846784, V_{GS} = -1.9677902268 \right\} ,  \left\{ I_{D} = 0.0021330175, V_{GS} = -4.7444709117 \right\}  \right\} </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> \left\{  \left\{ I_{D} = 0.0009058569, V_{GS} = -2.0050236605 \right\} ,  \left\{ I_{D} = 0.0020917696, V_{GS} = -4.6299227377 \right\}  \right\} </t>
-  </si>
-  <si>
     <t>Solved equations using CAS and measured values for each Q, this gives two solutions for each Q but one is outside VGSoff so is not used</t>
   </si>
   <si>
@@ -173,9 +167,6 @@
     <t>ID = VS/RS</t>
   </si>
   <si>
-    <t>VCC</t>
-  </si>
-  <si>
     <t>Part 3</t>
   </si>
   <si>
@@ -240,6 +231,21 @@
   </si>
   <si>
     <t>Av = Av1 * Av2</t>
+  </si>
+  <si>
+    <t>{{I_{D1} = 0.002449451023818, V_{GS1} = -1.245594834632}, {I_{D1} = 0.01473946603622, V_{GS1} = -7.495313268736}}</t>
+  </si>
+  <si>
+    <t>{{I_{D2} = 0.002555761292211, V_{GS2} = -1.296921067733}, {I_{D2} = 0.0141054336904, V_{GS2} = -7.157802326193}}</t>
+  </si>
+  <si>
+    <t>VDD 20V</t>
+  </si>
+  <si>
+    <t>Difference %</t>
+  </si>
+  <si>
+    <t>difference %</t>
   </si>
 </sst>
 </file>
@@ -619,7 +625,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC8C893E-9433-824B-8FC5-F5D257C12A0C}">
-  <dimension ref="A1:D80"/>
+  <dimension ref="A1:D95"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.5" customWidth="1"/>
@@ -870,21 +876,21 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>26</v>
+        <v>67</v>
       </c>
       <c r="B31">
-        <v>1021500</v>
+        <v>19.98</v>
       </c>
       <c r="C31" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B32">
-        <v>1016400</v>
+        <v>1021500</v>
       </c>
       <c r="C32" t="s">
         <v>1</v>
@@ -892,47 +898,44 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
+        <v>27</v>
+      </c>
+      <c r="B33">
+        <v>1016400</v>
+      </c>
+      <c r="C33" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
         <v>28</v>
       </c>
-      <c r="B33">
+      <c r="B34">
         <f>B2</f>
         <v>508.52</v>
       </c>
-      <c r="C33" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
-        <v>30</v>
-      </c>
-      <c r="B34">
-        <v>507.45</v>
-      </c>
       <c r="C34" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B35">
-        <v>2224.3000000000002</v>
+        <v>507.45</v>
       </c>
       <c r="C35" t="s">
         <v>1</v>
       </c>
-      <c r="D35" t="s">
-        <v>31</v>
-      </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B36">
-        <v>2213.4</v>
+        <v>2224.3000000000002</v>
       </c>
       <c r="C36" t="s">
         <v>1</v>
@@ -943,121 +946,124 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B37">
-        <v>9889.1</v>
+        <v>2213.4</v>
       </c>
       <c r="C37" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A39" t="s">
-        <v>39</v>
+      <c r="D37" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>29</v>
+      </c>
+      <c r="B38">
+        <v>9889.1</v>
+      </c>
+      <c r="C38" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>15</v>
-      </c>
-      <c r="B41">
-        <v>8.8467839999999999E-4</v>
-      </c>
-      <c r="C41" t="s">
-        <v>9</v>
-      </c>
-      <c r="D41" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="B42">
-        <v>-1.9677902268</v>
+        <v>2.4494510238180001E-3</v>
       </c>
       <c r="C42" t="s">
-        <v>6</v>
+        <v>9</v>
+      </c>
+      <c r="D42" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="B43">
-        <f>B6-(B41*B35)</f>
-        <v>8.0622098348799991</v>
+        <v>-1.245594834632</v>
       </c>
       <c r="C43" t="s">
         <v>6</v>
-      </c>
-      <c r="D43" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>36</v>
+        <v>14</v>
+      </c>
+      <c r="B44">
+        <f>B31-(B42*B36)</f>
+        <v>14.531686087721623</v>
+      </c>
+      <c r="C44" t="s">
+        <v>6</v>
+      </c>
+      <c r="D44" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>15</v>
-      </c>
-      <c r="B45">
-        <v>9.058569E-4</v>
-      </c>
-      <c r="C45" t="s">
-        <v>9</v>
-      </c>
-      <c r="D45" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="B46">
-        <v>-2.0050236605</v>
+        <v>2.5557612922109999E-3</v>
       </c>
       <c r="C46" t="s">
-        <v>6</v>
+        <v>9</v>
+      </c>
+      <c r="D46" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
+        <v>35</v>
+      </c>
+      <c r="B47">
+        <v>-1.2969210677330001</v>
+      </c>
+      <c r="C47" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
         <v>14</v>
       </c>
-      <c r="B47">
-        <f>B6-(B45*B36)</f>
-        <v>8.0249763375400001</v>
-      </c>
-      <c r="C47" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A49" t="s">
-        <v>41</v>
+      <c r="B48">
+        <f>B31-(B46*B37)</f>
+        <v>14.323077955820173</v>
+      </c>
+      <c r="C48" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>45</v>
-      </c>
-      <c r="B50">
-        <v>19.98</v>
-      </c>
-      <c r="C50" t="s">
-        <v>6</v>
+        <v>39</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
@@ -1067,7 +1073,7 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B52">
         <v>5.0000000000000001E-4</v>
@@ -1078,7 +1084,7 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B53">
         <v>1.2749999999999999</v>
@@ -1114,14 +1120,14 @@
         <v>15</v>
       </c>
       <c r="B56">
-        <f>B53/B33</f>
+        <f>B53/B34</f>
         <v>2.5072760166758436E-3</v>
       </c>
       <c r="C56" t="s">
         <v>9</v>
       </c>
       <c r="D56" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
@@ -1131,7 +1137,7 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B58">
         <v>5.9999999999999995E-4</v>
@@ -1142,7 +1148,7 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B59">
         <v>1.4590000000000001</v>
@@ -1178,7 +1184,7 @@
         <v>15</v>
       </c>
       <c r="B62">
-        <f>B59/B34</f>
+        <f>B59/B35</f>
         <v>2.8751601142969754E-3</v>
       </c>
       <c r="C62" t="s">
@@ -1190,193 +1196,294 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="B66">
+        <f>100*((B56-B42)/B42)</f>
+        <v>2.3607327640178992</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
+        <v>35</v>
+      </c>
+      <c r="B67">
+        <f>100*((B55-B43)/B43)</f>
+        <v>-1.4125648359161915</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
+        <v>14</v>
+      </c>
+      <c r="B68">
+        <f>100*((B54-B44)/B44)</f>
+        <v>-0.90619964487733307</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
+        <v>15</v>
+      </c>
+      <c r="B70">
+        <f>100*((B62-B46)/B46)</f>
+        <v>12.497208681396932</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
+        <v>35</v>
+      </c>
+      <c r="B71">
+        <f>100*((B61-B47)/B47)</f>
+        <v>-4.9286783385154758</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A72" t="s">
+        <v>14</v>
+      </c>
+      <c r="B72">
+        <f>100*((B60-B48)/B48)</f>
+        <v>-4.9087071786443666</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A74" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A75" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A76" t="s">
+        <v>46</v>
+      </c>
+      <c r="B76">
         <f>((2*B22)/ABS(B28)*(1-B61/B28))</f>
         <v>3.0277417263339886E-3</v>
       </c>
-      <c r="C66" t="s">
-        <v>55</v>
-      </c>
-      <c r="D66" t="s">
+      <c r="C76" t="s">
+        <v>52</v>
+      </c>
+      <c r="D76" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
+        <v>45</v>
+      </c>
+      <c r="B77">
+        <f>B76*(1/(1/B37+1/B38))</f>
+        <v>5.4759617879294114</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D77" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A78" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A67" t="s">
-        <v>48</v>
-      </c>
-      <c r="B67">
-        <f>B66*(1/(1/B36+1/B37))</f>
-        <v>5.4759617879294114</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D67" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A68" t="s">
-        <v>50</v>
-      </c>
-      <c r="B68">
+      <c r="B78">
         <f>((2*B11)/ABS(B17)*(1-B55/B17))</f>
         <v>2.7330198751968353E-3</v>
       </c>
-      <c r="C68" t="s">
-        <v>55</v>
-      </c>
-      <c r="D68" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A69" t="s">
+      <c r="C78" t="s">
         <v>52</v>
       </c>
-      <c r="B69">
-        <f>B68*(1/(1/B35+1/B32))</f>
-        <v>6.0657816906371522</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D69" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A70" t="s">
-        <v>57</v>
-      </c>
-      <c r="B70">
-        <f>B67*B69</f>
-        <v>33.215988751850908</v>
-      </c>
-      <c r="D70" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A72" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A73" t="s">
-        <v>63</v>
-      </c>
-      <c r="B73">
-        <v>10</v>
-      </c>
-      <c r="C73" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A74" t="s">
-        <v>59</v>
-      </c>
-      <c r="B74">
-        <v>0.01</v>
-      </c>
-      <c r="C74" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A75" t="s">
-        <v>60</v>
-      </c>
-      <c r="B75">
-        <v>0.35599999999999998</v>
-      </c>
-      <c r="C75" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A76" t="s">
-        <v>57</v>
-      </c>
-      <c r="B76" s="4">
-        <f>B75/B74</f>
-        <v>35.599999999999994</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D76" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A77" t="s">
-        <v>62</v>
-      </c>
-      <c r="B77">
-        <v>6.3100000000000003E-2</v>
-      </c>
-      <c r="C77" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A78" t="s">
-        <v>52</v>
-      </c>
-      <c r="B78">
-        <f>B77/B74</f>
-        <v>6.3100000000000005</v>
-      </c>
-      <c r="C78" s="3" t="s">
-        <v>56</v>
-      </c>
       <c r="D78" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B79">
-        <f>B75/B77</f>
-        <v>5.6418383518225035</v>
+        <f>B78*(1/(1/B36+1/B33))</f>
+        <v>6.0657816906371522</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D79" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
+        <v>54</v>
+      </c>
+      <c r="B80">
+        <f>B77*B79</f>
+        <v>33.215988751850908</v>
+      </c>
+      <c r="D80" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A82" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A83" t="s">
+        <v>60</v>
+      </c>
+      <c r="B83">
+        <v>10</v>
+      </c>
+      <c r="C83" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A84" t="s">
+        <v>56</v>
+      </c>
+      <c r="B84">
+        <v>0.01</v>
+      </c>
+      <c r="C84" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A85" t="s">
         <v>57</v>
       </c>
-      <c r="B80" s="4">
-        <f>B78*B79</f>
+      <c r="B85">
+        <v>0.35599999999999998</v>
+      </c>
+      <c r="C85" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A86" t="s">
+        <v>54</v>
+      </c>
+      <c r="B86" s="4">
+        <f>B85/B84</f>
+        <v>35.599999999999994</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D86" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A87" t="s">
+        <v>59</v>
+      </c>
+      <c r="B87">
+        <v>6.3100000000000003E-2</v>
+      </c>
+      <c r="C87" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A88" t="s">
+        <v>49</v>
+      </c>
+      <c r="B88">
+        <f>B87/B84</f>
+        <v>6.3100000000000005</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D88" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A89" t="s">
+        <v>45</v>
+      </c>
+      <c r="B89">
+        <f>B85/B87</f>
+        <v>5.6418383518225035</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D89" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A90" t="s">
+        <v>54</v>
+      </c>
+      <c r="B90" s="4">
+        <f>B88*B89</f>
         <v>35.6</v>
       </c>
-      <c r="C80" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D80" t="s">
-        <v>67</v>
+      <c r="C90" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D90" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A92" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A93" t="s">
+        <v>49</v>
+      </c>
+      <c r="B93">
+        <f>100*((B88-B79)/B79)</f>
+        <v>4.02616384529321</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A94" t="s">
+        <v>45</v>
+      </c>
+      <c r="B94">
+        <f>100*((B89-B77)/B77)</f>
+        <v>3.0291767970100083</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A95" t="s">
+        <v>54</v>
+      </c>
+      <c r="B95">
+        <f>100*((B86-B80)/B80)</f>
+        <v>7.1773002633144287</v>
       </c>
     </row>
   </sheetData>
